--- a/insurance_forms/006_flood_insurance_decision_making_quiz--insurance_forms.xlsx
+++ b/insurance_forms/006_flood_insurance_decision_making_quiz--insurance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_your_current_address</t>
+          <t>Current Address</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what_type_of_property_do_you_own</t>
+          <t>Property Type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>what_is_your_annual_income</t>
+          <t>Annual Income</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>how_important_is_flood_insurance_to_you</t>
+          <t>Importance Of Flood Insurance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>do_you_have_any_flood_insurance_policy</t>
+          <t>Flood Insurance Policy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>what_is_your_current_level_of_knowledge_about_flood_insurance</t>
+          <t>Level Of Knowledge</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>how_much_do_you_know_about_flood_zones_or_flood_maps</t>
+          <t>Flood Zones</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>how_much_do_you_know_about_flood_insurance_coverage_and_costs</t>
+          <t>Flood Insurance Coverage</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>would_you_like_to_learn_more_about_flood_insurance</t>
+          <t>Want To Learn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>would_you_like_to_receive_more_information_about_flood_insurance</t>
+          <t>Receive More Info</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
